--- a/artfynd/S 4751-2022 artfynd.xlsx
+++ b/artfynd/S 4751-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17109731</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17109769</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17109775</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110698</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1191,6 +1216,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83571828</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1306,6 +1336,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83571856</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1407,6 +1442,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17109693</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1508,6 +1548,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17109701</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1609,6 +1654,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17109716</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1710,6 +1760,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17109724</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1811,6 +1866,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17109779</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1912,6 +1972,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17109792</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2013,6 +2078,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17109797</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2114,6 +2184,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17109829</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2215,6 +2290,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17109899</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2316,6 +2396,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110375</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2417,6 +2502,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110379</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2518,6 +2608,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110407</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2619,6 +2714,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110441</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2720,6 +2820,11 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110472</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2835,6 +2940,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83571794</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2950,6 +3060,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83571797</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3065,6 +3180,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83571811</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3180,6 +3300,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83571820</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3295,6 +3420,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83571829</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3410,6 +3540,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83571858</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3525,6 +3660,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83571862</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3640,6 +3780,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83571865</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3755,6 +3900,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83571887</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3870,6 +4020,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83571938</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3971,8 +4126,46 @@
           <t>Inventering skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17110895</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>